--- a/main/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6005" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6005" uniqueCount="608">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -491,6 +491,10 @@
     <t>Procedure.extension.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -549,14 +553,10 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
   </si>
   <si>
     <t>Procedure.extension:difficulte</t>
@@ -943,10 +943,6 @@
     <t>Procedure.recorder.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Procedure.recorder.extension</t>
   </si>
   <si>
@@ -1015,9 +1011,6 @@
   </si>
   <si>
     <t>Procedure.recorder.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>AUT</t>
@@ -3506,7 +3499,7 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>138</v>
@@ -3552,13 +3545,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>89</v>
+        <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3609,7 +3602,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3618,7 +3611,7 @@
         <v>87</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>77</v>
@@ -3627,7 +3620,7 @@
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -3638,10 +3631,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3712,7 +3705,7 @@
         <v>135</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>77</v>
@@ -3721,7 +3714,7 @@
         <v>136</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3750,10 +3743,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3779,13 +3772,13 @@
         <v>101</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3793,7 +3786,7 @@
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>77</v>
@@ -3835,7 +3828,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>87</v>
@@ -3864,10 +3857,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3890,13 +3883,13 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3947,7 +3940,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3956,7 +3949,7 @@
         <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>99</v>
@@ -5706,13 +5699,13 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5763,7 +5756,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5781,7 +5774,7 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -5792,10 +5785,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5821,10 +5814,10 @@
         <v>132</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>183</v>
@@ -5868,7 +5861,7 @@
         <v>135</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>77</v>
@@ -5877,7 +5870,7 @@
         <v>136</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5895,7 +5888,7 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5906,13 +5899,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="C33" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>77</v>
@@ -5934,13 +5927,13 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5991,7 +5984,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6020,10 +6013,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6046,13 +6039,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6103,7 +6096,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6121,7 +6114,7 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -6132,10 +6125,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6143,7 +6136,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>79</v>
@@ -6206,7 +6199,7 @@
         <v>135</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>77</v>
@@ -6215,7 +6208,7 @@
         <v>136</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6244,13 +6237,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="C36" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>77</v>
@@ -6329,7 +6322,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6358,10 +6351,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6384,13 +6377,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6441,7 +6434,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6459,7 +6452,7 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -6470,10 +6463,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6544,7 +6537,7 @@
         <v>135</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>77</v>
@@ -6553,7 +6546,7 @@
         <v>136</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6582,10 +6575,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B39" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6611,13 +6604,13 @@
         <v>101</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6625,7 +6618,7 @@
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>77</v>
@@ -6667,7 +6660,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>87</v>
@@ -6696,10 +6689,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6725,10 +6718,10 @@
         <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6740,7 +6733,7 @@
         <v>77</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>77</v>
@@ -6759,7 +6752,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -6777,7 +6770,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6806,13 +6799,13 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>77</v>
@@ -6837,7 +6830,7 @@
         <v>132</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M41" t="s" s="2">
         <v>134</v>
@@ -6891,7 +6884,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6920,10 +6913,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6946,13 +6939,13 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7003,7 +6996,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7021,7 +7014,7 @@
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -7032,10 +7025,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7106,7 +7099,7 @@
         <v>135</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>77</v>
@@ -7115,7 +7108,7 @@
         <v>136</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7144,10 +7137,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7173,13 +7166,13 @@
         <v>101</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7187,7 +7180,7 @@
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>77</v>
@@ -7229,7 +7222,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -7258,10 +7251,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7287,10 +7280,10 @@
         <v>234</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7341,7 +7334,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7370,13 +7363,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>77</v>
@@ -7455,7 +7448,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7484,10 +7477,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7510,13 +7503,13 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7567,7 +7560,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7585,7 +7578,7 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7596,10 +7589,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7670,7 +7663,7 @@
         <v>135</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>77</v>
@@ -7679,7 +7672,7 @@
         <v>136</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7708,10 +7701,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7737,13 +7730,13 @@
         <v>101</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7751,7 +7744,7 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>77</v>
@@ -7793,7 +7786,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>87</v>
@@ -7822,10 +7815,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7848,13 +7841,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7905,7 +7898,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7934,10 +7927,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7963,13 +7956,13 @@
         <v>101</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7977,7 +7970,7 @@
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>77</v>
@@ -8019,7 +8012,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>87</v>
@@ -8048,10 +8041,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8074,13 +8067,13 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8131,7 +8124,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8160,10 +8153,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8186,16 +8179,16 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8245,7 +8238,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8254,7 +8247,7 @@
         <v>87</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>99</v>
@@ -8274,10 +8267,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8303,13 +8296,13 @@
         <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8335,31 +8328,31 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="Z54" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="Y54" t="s" s="2">
+      <c r="AA54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8388,10 +8381,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8417,13 +8410,13 @@
         <v>187</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8473,7 +8466,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8491,7 +8484,7 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8502,10 +8495,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8528,16 +8521,16 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8587,7 +8580,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8616,10 +8609,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8645,10 +8638,10 @@
         <v>289</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8699,7 +8692,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8717,10 +8710,10 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8728,10 +8721,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8754,13 +8747,13 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8811,7 +8804,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8826,10 +8819,10 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8840,10 +8833,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8866,13 +8859,13 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8923,7 +8916,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8941,7 +8934,7 @@
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
@@ -8952,10 +8945,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8981,10 +8974,10 @@
         <v>132</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>183</v>
@@ -9037,7 +9030,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9055,7 +9048,7 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -9066,14 +9059,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9095,10 +9088,10 @@
         <v>132</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>183</v>
@@ -9153,7 +9146,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9182,10 +9175,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9211,14 +9204,14 @@
         <v>234</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9246,10 +9239,10 @@
         <v>238</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>77</v>
@@ -9267,7 +9260,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9282,24 +9275,24 @@
         <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>393</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9322,17 +9315,17 @@
         <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9381,7 +9374,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>87</v>
@@ -9396,24 +9389,24 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>402</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9436,13 +9429,13 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9493,7 +9486,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9511,7 +9504,7 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -9522,10 +9515,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9551,10 +9544,10 @@
         <v>132</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>183</v>
@@ -9598,7 +9591,7 @@
         <v>135</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>77</v>
@@ -9607,7 +9600,7 @@
         <v>136</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9625,7 +9618,7 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -9636,13 +9629,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B66" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C66" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>77</v>
@@ -9664,13 +9657,13 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9721,7 +9714,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9750,10 +9743,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9776,13 +9769,13 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9833,7 +9826,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9851,7 +9844,7 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -9862,10 +9855,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9873,7 +9866,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>79</v>
@@ -9936,7 +9929,7 @@
         <v>135</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>77</v>
@@ -9945,7 +9938,7 @@
         <v>136</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9974,13 +9967,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>77</v>
@@ -10059,7 +10052,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10088,10 +10081,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10114,13 +10107,13 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10171,7 +10164,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10189,7 +10182,7 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -10200,10 +10193,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10274,7 +10267,7 @@
         <v>135</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>77</v>
@@ -10283,7 +10276,7 @@
         <v>136</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10312,10 +10305,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10341,13 +10334,13 @@
         <v>101</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10355,7 +10348,7 @@
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>77</v>
@@ -10397,7 +10390,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>87</v>
@@ -10426,10 +10419,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10455,10 +10448,10 @@
         <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10470,7 +10463,7 @@
         <v>77</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>77</v>
@@ -10489,7 +10482,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>77</v>
@@ -10507,7 +10500,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10536,13 +10529,13 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>77</v>
@@ -10567,7 +10560,7 @@
         <v>132</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M74" t="s" s="2">
         <v>134</v>
@@ -10621,7 +10614,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10650,10 +10643,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10676,13 +10669,13 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10733,7 +10726,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10751,7 +10744,7 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
@@ -10762,10 +10755,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10836,7 +10829,7 @@
         <v>135</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>77</v>
@@ -10845,7 +10838,7 @@
         <v>136</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10874,10 +10867,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10903,13 +10896,13 @@
         <v>101</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10917,7 +10910,7 @@
       </c>
       <c r="Q77" s="2"/>
       <c r="R77" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="S77" t="s" s="2">
         <v>77</v>
@@ -10959,7 +10952,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>87</v>
@@ -10988,10 +10981,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11017,10 +11010,10 @@
         <v>234</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11071,7 +11064,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11100,13 +11093,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>77</v>
@@ -11185,7 +11178,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11214,10 +11207,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11240,13 +11233,13 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11297,7 +11290,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11315,7 +11308,7 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -11326,10 +11319,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11400,7 +11393,7 @@
         <v>135</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>77</v>
@@ -11409,7 +11402,7 @@
         <v>136</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11438,10 +11431,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11467,13 +11460,13 @@
         <v>101</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11481,7 +11474,7 @@
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>77</v>
@@ -11523,7 +11516,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>87</v>
@@ -11552,10 +11545,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11578,13 +11571,13 @@
         <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11635,7 +11628,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11664,10 +11657,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11693,13 +11686,13 @@
         <v>101</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11707,7 +11700,7 @@
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>77</v>
@@ -11749,7 +11742,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>87</v>
@@ -11778,10 +11771,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11804,13 +11797,13 @@
         <v>77</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11861,7 +11854,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11890,13 +11883,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>77</v>
@@ -11918,13 +11911,13 @@
         <v>77</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11975,7 +11968,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12004,10 +11997,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12030,13 +12023,13 @@
         <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12087,7 +12080,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12105,7 +12098,7 @@
         <v>77</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -12116,10 +12109,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12127,7 +12120,7 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>79</v>
@@ -12190,7 +12183,7 @@
         <v>135</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>77</v>
@@ -12199,7 +12192,7 @@
         <v>136</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12228,13 +12221,13 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>77</v>
@@ -12313,7 +12306,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12342,10 +12335,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12368,13 +12361,13 @@
         <v>77</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12425,7 +12418,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12443,7 +12436,7 @@
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -12454,10 +12447,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12528,7 +12521,7 @@
         <v>135</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>77</v>
@@ -12537,7 +12530,7 @@
         <v>136</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12566,10 +12559,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12595,13 +12588,13 @@
         <v>101</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12609,7 +12602,7 @@
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>77</v>
@@ -12651,7 +12644,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>87</v>
@@ -12680,10 +12673,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12709,10 +12702,10 @@
         <v>107</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12724,7 +12717,7 @@
         <v>77</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>77</v>
@@ -12743,7 +12736,7 @@
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>77</v>
@@ -12761,7 +12754,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12790,13 +12783,13 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>77</v>
@@ -12821,7 +12814,7 @@
         <v>132</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M94" t="s" s="2">
         <v>134</v>
@@ -12875,7 +12868,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12904,10 +12897,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12930,13 +12923,13 @@
         <v>77</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12987,7 +12980,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13005,7 +12998,7 @@
         <v>77</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
@@ -13016,10 +13009,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13090,7 +13083,7 @@
         <v>135</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>77</v>
@@ -13099,7 +13092,7 @@
         <v>136</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13128,10 +13121,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13157,13 +13150,13 @@
         <v>101</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13171,7 +13164,7 @@
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>77</v>
@@ -13213,7 +13206,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>87</v>
@@ -13242,10 +13235,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13271,10 +13264,10 @@
         <v>234</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13325,7 +13318,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13354,13 +13347,13 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>77</v>
@@ -13439,7 +13432,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13468,10 +13461,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13494,13 +13487,13 @@
         <v>77</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13551,7 +13544,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13569,7 +13562,7 @@
         <v>77</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>77</v>
@@ -13580,10 +13573,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13654,7 +13647,7 @@
         <v>135</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>77</v>
@@ -13663,7 +13656,7 @@
         <v>136</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13692,10 +13685,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13721,13 +13714,13 @@
         <v>101</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13735,7 +13728,7 @@
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="S102" t="s" s="2">
         <v>77</v>
@@ -13777,7 +13770,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>87</v>
@@ -13806,10 +13799,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13832,13 +13825,13 @@
         <v>77</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13889,7 +13882,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13918,10 +13911,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13947,13 +13940,13 @@
         <v>101</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -13961,7 +13954,7 @@
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>77</v>
@@ -14003,7 +13996,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>87</v>
@@ -14032,10 +14025,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14058,13 +14051,13 @@
         <v>77</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14115,7 +14108,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14144,13 +14137,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>77</v>
@@ -14172,13 +14165,13 @@
         <v>77</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14229,7 +14222,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14258,10 +14251,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14284,13 +14277,13 @@
         <v>77</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14341,7 +14334,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14359,7 +14352,7 @@
         <v>77</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>77</v>
@@ -14370,10 +14363,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14381,7 +14374,7 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>79</v>
@@ -14444,7 +14437,7 @@
         <v>135</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>77</v>
@@ -14453,7 +14446,7 @@
         <v>136</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -14482,13 +14475,13 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>77</v>
@@ -14567,7 +14560,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14596,10 +14589,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14622,13 +14615,13 @@
         <v>77</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14679,7 +14672,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14697,7 +14690,7 @@
         <v>77</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>77</v>
@@ -14708,10 +14701,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14782,7 +14775,7 @@
         <v>135</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>77</v>
@@ -14791,7 +14784,7 @@
         <v>136</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14820,10 +14813,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14849,13 +14842,13 @@
         <v>101</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14863,7 +14856,7 @@
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="S112" t="s" s="2">
         <v>77</v>
@@ -14905,7 +14898,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>87</v>
@@ -14934,10 +14927,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14963,10 +14956,10 @@
         <v>107</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -14978,7 +14971,7 @@
         <v>77</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>77</v>
@@ -14997,7 +14990,7 @@
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>77</v>
@@ -15015,7 +15008,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15044,13 +15037,13 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>77</v>
@@ -15075,7 +15068,7 @@
         <v>132</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M114" t="s" s="2">
         <v>134</v>
@@ -15129,7 +15122,7 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -15158,10 +15151,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15184,13 +15177,13 @@
         <v>77</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15241,7 +15234,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15259,7 +15252,7 @@
         <v>77</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>77</v>
@@ -15270,10 +15263,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15344,7 +15337,7 @@
         <v>135</v>
       </c>
       <c r="AC116" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD116" t="s" s="2">
         <v>77</v>
@@ -15353,7 +15346,7 @@
         <v>136</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -15382,10 +15375,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15411,13 +15404,13 @@
         <v>101</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15425,7 +15418,7 @@
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>77</v>
@@ -15467,7 +15460,7 @@
         <v>77</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>87</v>
@@ -15496,10 +15489,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15525,10 +15518,10 @@
         <v>234</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -15579,7 +15572,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -15608,13 +15601,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>77</v>
@@ -15693,7 +15686,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -15722,10 +15715,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15748,13 +15741,13 @@
         <v>77</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -15805,7 +15798,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15823,7 +15816,7 @@
         <v>77</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>77</v>
@@ -15834,10 +15827,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15908,7 +15901,7 @@
         <v>135</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>77</v>
@@ -15917,7 +15910,7 @@
         <v>136</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -15946,10 +15939,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15975,13 +15968,13 @@
         <v>101</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -15989,7 +15982,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>77</v>
@@ -16031,7 +16024,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>87</v>
@@ -16060,10 +16053,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16086,13 +16079,13 @@
         <v>77</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16143,7 +16136,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16172,10 +16165,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16201,13 +16194,13 @@
         <v>101</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -16215,7 +16208,7 @@
       </c>
       <c r="Q124" s="2"/>
       <c r="R124" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="S124" t="s" s="2">
         <v>77</v>
@@ -16257,7 +16250,7 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>87</v>
@@ -16286,10 +16279,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16312,13 +16305,13 @@
         <v>77</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -16369,7 +16362,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16398,13 +16391,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>77</v>
@@ -16426,13 +16419,13 @@
         <v>77</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16483,7 +16476,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16512,10 +16505,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16538,13 +16531,13 @@
         <v>77</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -16595,7 +16588,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -16613,7 +16606,7 @@
         <v>77</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>77</v>
@@ -16624,10 +16617,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16635,7 +16628,7 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G128" t="s" s="2">
         <v>79</v>
@@ -16698,7 +16691,7 @@
         <v>135</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>77</v>
@@ -16707,7 +16700,7 @@
         <v>136</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -16736,13 +16729,13 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>77</v>
@@ -16821,7 +16814,7 @@
         <v>77</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -16850,10 +16843,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16876,13 +16869,13 @@
         <v>77</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -16933,7 +16926,7 @@
         <v>77</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
@@ -16951,7 +16944,7 @@
         <v>77</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>77</v>
@@ -16962,10 +16955,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17036,7 +17029,7 @@
         <v>135</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>77</v>
@@ -17045,7 +17038,7 @@
         <v>136</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -17074,10 +17067,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17103,13 +17096,13 @@
         <v>101</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -17117,7 +17110,7 @@
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>77</v>
@@ -17159,7 +17152,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>87</v>
@@ -17188,10 +17181,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17217,10 +17210,10 @@
         <v>107</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -17232,7 +17225,7 @@
         <v>77</v>
       </c>
       <c r="S133" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="T133" t="s" s="2">
         <v>77</v>
@@ -17251,7 +17244,7 @@
       </c>
       <c r="Y133" s="2"/>
       <c r="Z133" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>77</v>
@@ -17269,7 +17262,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -17298,13 +17291,13 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D134" t="s" s="2">
         <v>77</v>
@@ -17329,7 +17322,7 @@
         <v>132</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M134" t="s" s="2">
         <v>134</v>
@@ -17383,7 +17376,7 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -17412,10 +17405,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17438,13 +17431,13 @@
         <v>77</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -17495,7 +17488,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -17513,7 +17506,7 @@
         <v>77</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>77</v>
@@ -17524,10 +17517,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17598,7 +17591,7 @@
         <v>135</v>
       </c>
       <c r="AC136" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD136" t="s" s="2">
         <v>77</v>
@@ -17607,7 +17600,7 @@
         <v>136</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -17636,10 +17629,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17665,13 +17658,13 @@
         <v>101</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -17679,7 +17672,7 @@
       </c>
       <c r="Q137" s="2"/>
       <c r="R137" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="S137" t="s" s="2">
         <v>77</v>
@@ -17721,7 +17714,7 @@
         <v>77</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>87</v>
@@ -17750,10 +17743,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17779,10 +17772,10 @@
         <v>234</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -17833,7 +17826,7 @@
         <v>77</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>78</v>
@@ -17862,13 +17855,13 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>77</v>
@@ -17947,7 +17940,7 @@
         <v>77</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>78</v>
@@ -17976,10 +17969,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18002,13 +17995,13 @@
         <v>77</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -18059,7 +18052,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -18077,7 +18070,7 @@
         <v>77</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>77</v>
@@ -18088,10 +18081,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18162,7 +18155,7 @@
         <v>135</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>77</v>
@@ -18171,7 +18164,7 @@
         <v>136</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -18200,10 +18193,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18229,13 +18222,13 @@
         <v>101</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -18243,7 +18236,7 @@
       </c>
       <c r="Q142" s="2"/>
       <c r="R142" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="S142" t="s" s="2">
         <v>77</v>
@@ -18285,7 +18278,7 @@
         <v>77</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>87</v>
@@ -18314,10 +18307,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18340,13 +18333,13 @@
         <v>77</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -18397,7 +18390,7 @@
         <v>77</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -18426,10 +18419,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18455,13 +18448,13 @@
         <v>101</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -18469,7 +18462,7 @@
       </c>
       <c r="Q144" s="2"/>
       <c r="R144" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="S144" t="s" s="2">
         <v>77</v>
@@ -18511,7 +18504,7 @@
         <v>77</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>87</v>
@@ -18540,10 +18533,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18566,13 +18559,13 @@
         <v>77</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -18623,7 +18616,7 @@
         <v>77</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
@@ -18652,10 +18645,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18678,16 +18671,16 @@
         <v>88</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="N146" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -18737,7 +18730,7 @@
         <v>77</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>78</v>
@@ -18746,7 +18739,7 @@
         <v>87</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AJ146" t="s" s="2">
         <v>99</v>
@@ -18766,10 +18759,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18795,13 +18788,13 @@
         <v>101</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="N147" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -18827,31 +18820,31 @@
         <v>77</v>
       </c>
       <c r="X147" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="Z147" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="Y147" t="s" s="2">
+      <c r="AA147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF147" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="Z147" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AA147" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB147" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC147" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD147" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE147" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF147" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -18880,10 +18873,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -18909,13 +18902,13 @@
         <v>187</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N148" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -18965,7 +18958,7 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -18983,7 +18976,7 @@
         <v>77</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>77</v>
@@ -18994,10 +18987,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19020,16 +19013,16 @@
         <v>88</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N149" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -19079,7 +19072,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -19108,10 +19101,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19134,17 +19127,17 @@
         <v>77</v>
       </c>
       <c r="K150" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L150" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="L150" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>77</v>
@@ -19193,7 +19186,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -19211,7 +19204,7 @@
         <v>77</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>77</v>
@@ -19222,10 +19215,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19248,17 +19241,17 @@
         <v>88</v>
       </c>
       <c r="K151" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="L151" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="L151" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>77</v>
@@ -19307,7 +19300,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -19325,10 +19318,10 @@
         <v>77</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>77</v>
@@ -19336,10 +19329,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19365,13 +19358,13 @@
         <v>234</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N152" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -19400,10 +19393,10 @@
         <v>238</v>
       </c>
       <c r="Y152" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="Z152" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>77</v>
@@ -19421,7 +19414,7 @@
         <v>77</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -19436,13 +19429,13 @@
         <v>99</v>
       </c>
       <c r="AK152" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AM152" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AL152" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AM152" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>77</v>
@@ -19450,10 +19443,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19476,16 +19469,16 @@
         <v>88</v>
       </c>
       <c r="K153" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="L153" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="L153" t="s" s="2">
+      <c r="N153" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -19535,7 +19528,7 @@
         <v>77</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>78</v>
@@ -19550,13 +19543,13 @@
         <v>99</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>77</v>
@@ -19564,10 +19557,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19593,13 +19586,13 @@
         <v>234</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N154" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -19625,11 +19618,11 @@
         <v>77</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="Y154" s="2"/>
       <c r="Z154" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>77</v>
@@ -19647,7 +19640,7 @@
         <v>77</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>78</v>
@@ -19665,21 +19658,21 @@
         <v>77</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -19705,13 +19698,13 @@
         <v>234</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M155" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="N155" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -19740,10 +19733,10 @@
         <v>238</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>77</v>
@@ -19761,7 +19754,7 @@
         <v>77</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>78</v>
@@ -19779,7 +19772,7 @@
         <v>77</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AM155" t="s" s="2">
         <v>77</v>
@@ -19790,10 +19783,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -19816,16 +19809,16 @@
         <v>77</v>
       </c>
       <c r="K156" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="L156" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M156" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="L156" t="s" s="2">
+      <c r="N156" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -19875,7 +19868,7 @@
         <v>77</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>78</v>
@@ -19893,7 +19886,7 @@
         <v>77</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>77</v>
@@ -19904,10 +19897,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -19933,13 +19926,13 @@
         <v>234</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M157" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="N157" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -19968,10 +19961,10 @@
         <v>238</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>77</v>
@@ -19989,7 +19982,7 @@
         <v>77</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>78</v>
@@ -20007,7 +20000,7 @@
         <v>77</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>77</v>
@@ -20018,10 +20011,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20044,17 +20037,17 @@
         <v>77</v>
       </c>
       <c r="K158" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="L158" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="L158" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>77</v>
@@ -20103,7 +20096,7 @@
         <v>77</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -20121,7 +20114,7 @@
         <v>77</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AM158" t="s" s="2">
         <v>77</v>
@@ -20132,10 +20125,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20161,10 +20154,10 @@
         <v>234</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -20194,10 +20187,10 @@
         <v>238</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>77</v>
@@ -20215,7 +20208,7 @@
         <v>77</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>78</v>
@@ -20233,7 +20226,7 @@
         <v>77</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>77</v>
@@ -20244,10 +20237,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20270,13 +20263,13 @@
         <v>77</v>
       </c>
       <c r="K160" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="L160" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="L160" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -20327,7 +20320,7 @@
         <v>77</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>78</v>
@@ -20342,24 +20335,24 @@
         <v>99</v>
       </c>
       <c r="AK160" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AL160" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AM160" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN160" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="AL160" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="AM160" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN160" t="s" s="2">
-        <v>579</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20382,13 +20375,13 @@
         <v>77</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -20439,7 +20432,7 @@
         <v>77</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>78</v>
@@ -20457,7 +20450,7 @@
         <v>77</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>77</v>
@@ -20468,10 +20461,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20494,13 +20487,13 @@
         <v>77</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>295</v>
+        <v>152</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -20551,7 +20544,7 @@
         <v>77</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>78</v>
@@ -20569,7 +20562,7 @@
         <v>77</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM162" t="s" s="2">
         <v>77</v>
@@ -20580,10 +20573,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20609,10 +20602,10 @@
         <v>132</v>
       </c>
       <c r="L163" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M163" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="M163" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="N163" t="s" s="2">
         <v>183</v>
@@ -20665,7 +20658,7 @@
         <v>77</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>78</v>
@@ -20683,7 +20676,7 @@
         <v>77</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>77</v>
@@ -20694,14 +20687,14 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
@@ -20723,10 +20716,10 @@
         <v>132</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="N164" t="s" s="2">
         <v>183</v>
@@ -20781,7 +20774,7 @@
         <v>77</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -20810,10 +20803,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20839,10 +20832,10 @@
         <v>234</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -20872,10 +20865,10 @@
         <v>111</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>77</v>
@@ -20893,7 +20886,7 @@
         <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>78</v>
@@ -20911,7 +20904,7 @@
         <v>77</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>77</v>
@@ -20922,10 +20915,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -20948,13 +20941,13 @@
         <v>77</v>
       </c>
       <c r="K166" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="L166" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="L166" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -21005,7 +20998,7 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>87</v>
@@ -21023,7 +21016,7 @@
         <v>77</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>77</v>
@@ -21034,10 +21027,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21060,19 +21053,19 @@
         <v>77</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M167" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="N167" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="M167" t="s" s="2">
+      <c r="O167" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>77</v>
@@ -21121,7 +21114,7 @@
         <v>77</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>78</v>
@@ -21139,7 +21132,7 @@
         <v>77</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AM167" t="s" s="2">
         <v>77</v>
@@ -21150,10 +21143,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21179,13 +21172,13 @@
         <v>234</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -21214,10 +21207,10 @@
         <v>238</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>77</v>
@@ -21235,7 +21228,7 @@
         <v>77</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>78</v>
@@ -21253,7 +21246,7 @@
         <v>77</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="AM168" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
